--- a/output/stock_quant_scores/PLTR_balance_df.xlsx
+++ b/output/stock_quant_scores/PLTR_balance_df.xlsx
@@ -1482,30 +1482,40 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>260073000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>2203189000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>2291030000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-5485733000</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>956420000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
@@ -1518,7 +1528,9 @@
       <c r="AF6" t="n">
         <v>197977000</v>
       </c>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>660061000</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1528,7 +1540,9 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>3247450000</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
@@ -1539,7 +1553,9 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>2863250000</v>
+      </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>37285000</v>
@@ -1553,7 +1569,9 @@
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>2290674000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
